--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
@@ -8306,7 +8306,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
@@ -8306,7 +8306,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260512_211213.xlsx
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
